--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit5.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit5.xlsx
@@ -712,22 +712,22 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
+          <t>要加感嘆號</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>要感性</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
           <t>簡明扼要，概括核心內容</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>越長越好</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>要感性</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>要加感嘆號</t>
         </is>
       </c>
       <c r="G9" s="22" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -751,22 +751,22 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>請注意！！！</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
           <t>關於營業時間調整嘅通知</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>請注意！！！</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>update</t>
         </is>
       </c>
       <c r="G10" s="25" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -790,12 +790,12 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
+          <t>各位同事：您好！我係店務助理小儀，現將12月1日起嘅新營業時間安排通知如下。</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
           <t>您好！我係店務助理小儀，現將12月1日起嘅新營業時間安排通知如下。各位同事：</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>各位同事：您好！我係店務助理小儀，現將12月1日起嘅新營業時間安排通知如下。</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -825,17 +825,17 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
+          <t>提醒事項</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
           <t>12日・會議調動</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>13日・接待團</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>提醒事項</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -864,22 +864,22 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
+          <t>覆我！</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>記得覆我啊</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
           <t>煩請 閣下於明日內回覆確認</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>記得覆我啊</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>唔好忘記！</t>
-        </is>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>覆我！</t>
         </is>
       </c>
       <c r="G13" s="25" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
+          <t>唔寫（無關／失禮）</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
           <t>可寫（一句背景）</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>唔寫（無關／失禮）</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr"/>
@@ -948,12 +948,12 @@
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
+          <t>吳女士</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
           <t>全體員工</t>
-        </is>
-      </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>吳女士</t>
         </is>
       </c>
       <c r="G15" s="25" t="n">
@@ -977,22 +977,22 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
+          <t>要回覆</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>要批核</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>要轉發</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
           <t>只需知悉，唔使執行</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>要回覆</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>要批核</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>要轉發</t>
         </is>
       </c>
       <c r="G16" s="25" t="n">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -1016,22 +1016,22 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
+          <t>關門一日</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>緊急緊急緊急</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
           <t>3月20日（週五）暫停營業安排</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>抱歉</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>緊急緊急緊急</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>關門一日</t>
         </is>
       </c>
       <c r="G17" s="25" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>就3月20日停水期間嘅服務安排，現致函說明。親愛嘅會員：您好！我係會籍事務組阿俊，</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
           <t>您好！我係會籍事務組阿俊，就3月20日停水期間嘅服務安排，現致函說明。親愛嘅會員：</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>親愛嘅會員：您好！我係會籍事務組阿俊，就3月20日停水期間嘅服務安排，現致函說明。</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>就3月20日停水期間嘅服務安排，現致函說明。親愛嘅會員：您好！我係會籍事務組阿俊，</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1090,22 +1090,22 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
+          <t>13日・接待團</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>唔寫</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
           <t>12日・會議調動</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>13日・接待團</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>提醒事項</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
-        <is>
-          <t>唔寫</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
+          <t>搬去7樓，知未</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>改地方</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
           <t>7樓啦得啦</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>改地方</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>搬去7樓，知未</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
+          <t>唔寫（無關／失禮）</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
           <t>可寫（一句背景）</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>唔寫（無關／失禮）</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
+          <t>唔使通知佢</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
           <t>收件者</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>密件副本唔放</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>唔使通知佢</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
@@ -1242,22 +1242,22 @@
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
+          <t>打感嘆號</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>留空</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>寫「有嘢」</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
           <t>標明目錄呢個文件名稱</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>留空</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>寫「有嘢」</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>打感嘆號</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" s="1" t="n"/>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
+          <t>你睇下</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
           <t>請確認展板尺寸圖則（截止4/8）</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>圖則</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>你睇下</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="1" t="n"/>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
+          <t>提醒事項</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
           <t>13日・接待團</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>提醒事項</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
+          <t>佢哋10點</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>10點到人就到</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
           <t>參觀團將於上午10時正抵達，煩請主持接待</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>10點到人就到</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>佢哋10點</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -1433,17 +1433,17 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>可寫（一句背景）</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>唔寫（無關／失禮）</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
           <t>必寫（執行需要）</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>可寫（一句背景）</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>唔寫（無關／失禮）</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1468,17 +1468,17 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>安排</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>通知通知！</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
           <t>方總監外出期間（11/12-13）代理工作安排</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>安排</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>通知通知！</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
